--- a/forms/app/peer_mentor_checklist.xlsx
+++ b/forms/app/peer_mentor_checklist.xlsx
@@ -18,12 +18,12 @@
     <t>form_title</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>list_name</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>form_id</t>
   </si>
   <si>
@@ -48,9 +48,57 @@
     <t>label::sw</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
     <t>Peer Mentor Checklist</t>
   </si>
   <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
     <t>peer_mentor_checklist</t>
   </si>
   <si>
@@ -96,63 +144,15 @@
     <t>chv_support_options</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
     <t>tech_team</t>
   </si>
   <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technology Team </t>
   </si>
   <si>
-    <t>begin group</t>
-  </si>
-  <si>
     <t xml:space="preserve">Timu ya Teknolojia </t>
   </si>
   <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
     <t>chmt</t>
   </si>
   <si>
@@ -180,22 +180,22 @@
     <t>solar_charging</t>
   </si>
   <si>
+    <t>user</t>
+  </si>
+  <si>
     <t>no_solar_charger</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>Does not have/need solar charger</t>
   </si>
   <si>
+    <t>contact_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hahitaji chaji ya sola </t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>contact_id</t>
   </si>
   <si>
     <t>Contact ID of the logged in user</t>
@@ -702,6 +702,10 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -710,10 +714,6 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font/>
     <font>
@@ -784,33 +784,33 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -829,7 +829,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -838,7 +838,7 @@
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1109,7 +1109,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -1117,62 +1117,62 @@
       <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>40</v>
+      <c r="E1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="12" t="b">
+      <c r="F2" s="11" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>61</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>62</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>8</v>
@@ -1293,7 +1293,7 @@
         <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1316,7 +1316,7 @@
         <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1499,8 +1499,8 @@
       <c r="S14" s="18"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="s">
-        <v>42</v>
+      <c r="A15" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>83</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="4" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="2"/>
@@ -1541,7 +1541,7 @@
         <v>90</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="20"/>
@@ -1585,7 +1585,7 @@
         <v>96</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F17" s="21"/>
       <c r="G17" s="20"/>
@@ -1629,7 +1629,7 @@
         <v>101</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="20"/>
@@ -1660,7 +1660,7 @@
       <c r="Z18" s="21"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B19" s="19" t="s">
@@ -1672,8 +1672,8 @@
       <c r="D19" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>16</v>
+      <c r="E19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="23" t="s">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="4"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -1763,8 +1763,8 @@
       <c r="B22" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="C22" s="4"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>119</v>
@@ -1791,7 +1791,7 @@
       <c r="D23" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="9"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="2"/>
       <c r="G23" s="27" t="s">
         <v>86</v>
@@ -1821,7 +1821,7 @@
         <v>125</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1850,15 +1850,15 @@
         <v>128</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F25" s="27" t="s">
         <v>129</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1881,13 +1881,13 @@
         <v>132</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1910,15 +1910,15 @@
         <v>128</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F27" s="27" t="s">
         <v>134</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1941,13 +1941,13 @@
         <v>137</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -1970,15 +1970,15 @@
         <v>128</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F29" s="27" t="s">
         <v>139</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -2001,7 +2001,7 @@
         <v>142</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -2030,15 +2030,15 @@
         <v>128</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F31" s="27" t="s">
         <v>144</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2061,7 +2061,7 @@
         <v>147</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2090,15 +2090,15 @@
         <v>128</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F33" s="27" t="s">
         <v>149</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2121,7 +2121,7 @@
         <v>152</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -2150,15 +2150,15 @@
         <v>128</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F35" s="27" t="s">
         <v>154</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -2174,8 +2174,8 @@
       <c r="B36" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="C36" s="4"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>155</v>
@@ -2231,7 +2231,7 @@
         <v>160</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -2260,15 +2260,15 @@
         <v>128</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F39" s="27" t="s">
         <v>162</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -2291,7 +2291,7 @@
         <v>165</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2320,15 +2320,15 @@
         <v>128</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F41" s="27" t="s">
         <v>167</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -2351,7 +2351,7 @@
         <v>170</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -2380,15 +2380,15 @@
         <v>128</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F43" s="27" t="s">
         <v>172</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -2398,27 +2398,27 @@
       <c r="Q43" s="2"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="9" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
+      <c r="A45" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>173</v>
       </c>
       <c r="C45" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="9" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
         <v>178</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2465,15 +2465,15 @@
         <v>128</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F47" s="27" t="s">
         <v>180</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -2496,7 +2496,7 @@
         <v>183</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2525,15 +2525,15 @@
         <v>128</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F49" s="27" t="s">
         <v>185</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -2556,7 +2556,7 @@
         <v>188</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -2585,15 +2585,15 @@
         <v>128</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F51" s="27" t="s">
         <v>190</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -2616,7 +2616,7 @@
         <v>193</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -2645,15 +2645,15 @@
         <v>128</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F53" s="27" t="s">
         <v>195</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -2663,47 +2663,47 @@
       <c r="Q53" s="2"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F56" s="8"/>
+      <c r="E56" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" s="9"/>
       <c r="I56" s="29" t="s">
         <v>202</v>
       </c>
@@ -2715,70 +2715,70 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E57" s="8" t="s">
-        <v>16</v>
+      <c r="E57" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>16</v>
+      <c r="E58" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>16</v>
+      <c r="E59" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="9" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2802,199 +2802,199 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>18</v>
+      <c r="A2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>21</v>
+      <c r="A3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>24</v>
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>18</v>
+      <c r="A5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>24</v>
+      <c r="A6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>43</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>17</v>
+      <c r="B11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>21</v>
+      <c r="B12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>24</v>
+      <c r="B13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>57</v>
+      <c r="C14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3054,17 +3054,17 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>

--- a/forms/app/peer_mentor_checklist.xlsx
+++ b/forms/app/peer_mentor_checklist.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="4425" windowHeight="2115"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="222">
   <si>
     <t>type</t>
   </si>
@@ -250,9 +258,6 @@
     <t>numbers</t>
   </si>
   <si>
-    <t>regex(.,'^0[0-9]{9}$')</t>
-  </si>
-  <si>
     <t>Use the following format 0XXXXXXXXX</t>
   </si>
   <si>
@@ -695,59 +700,71 @@
   </si>
   <si>
     <t>data</t>
+  </si>
+  <si>
+    <t>tel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="12">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
-      <sz val="12.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -757,7 +774,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -773,147 +790,97 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
+      <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1103,26 +1070,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z61"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.0"/>
-    <col customWidth="1" min="2" max="2" width="27.43"/>
-    <col customWidth="1" min="3" max="3" width="57.0"/>
-    <col customWidth="1" min="4" max="4" width="34.43"/>
-    <col customWidth="1" min="5" max="5" width="22.29"/>
-    <col customWidth="1" min="9" max="9" width="36.14"/>
-    <col customWidth="1" min="10" max="10" width="29.43"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="27.40625" customWidth="1"/>
+    <col min="3" max="3" width="57" customWidth="1"/>
+    <col min="4" max="4" width="34.40625" customWidth="1"/>
+    <col min="5" max="5" width="22.26953125" customWidth="1"/>
+    <col min="9" max="9" width="36.1328125" customWidth="1"/>
+    <col min="10" max="10" width="29.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="13">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1203,7 +1173,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="13">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1198,7 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="13">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1253,7 +1223,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="13">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -1278,7 +1248,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="13">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1303,7 +1273,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="13">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1326,7 +1296,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="13">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -1349,7 +1319,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="13">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -1376,7 +1346,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="13">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -1403,7 +1373,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="13">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1430,7 +1400,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="13">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -1462,7 +1432,7 @@
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="13">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -1494,7 +1464,7 @@
       <c r="Y13" s="10"/>
       <c r="Z13" s="10"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="13">
       <c r="A14" s="8" t="s">
         <v>38</v>
       </c>
@@ -1523,7 +1493,7 @@
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" ht="12.75" customHeight="1">
+    <row r="15" spans="1:26" ht="12.75" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
@@ -1552,7 +1522,7 @@
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="13">
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
@@ -1577,7 +1547,7 @@
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" ht="13">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -1606,7 +1576,7 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" ht="13">
       <c r="A18" s="13" t="s">
         <v>51</v>
       </c>
@@ -1650,7 +1620,7 @@
       <c r="Y18" s="14"/>
       <c r="Z18" s="14"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" ht="13">
       <c r="A19" s="13" t="s">
         <v>51</v>
       </c>
@@ -1694,7 +1664,7 @@
       <c r="Y19" s="14"/>
       <c r="Z19" s="14"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" ht="13">
       <c r="A20" s="13" t="s">
         <v>51</v>
       </c>
@@ -1738,9 +1708,9 @@
       <c r="Y20" s="14"/>
       <c r="Z20" s="14"/>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>51</v>
+    <row r="21" spans="1:26" ht="13">
+      <c r="A21" s="15" t="s">
+        <v>221</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>69</v>
@@ -1759,14 +1729,14 @@
         <v>72</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="K21" s="15" t="s">
         <v>74</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>75</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1775,21 +1745,21 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" ht="13">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B22" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="D22" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="E22" s="12" t="s">
         <v>78</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>79</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1798,10 +1768,10 @@
         <v>56</v>
       </c>
       <c r="J22" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>81</v>
       </c>
       <c r="L22" s="18"/>
       <c r="M22" s="1"/>
@@ -1810,14 +1780,15 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" ht="13">
       <c r="A23" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="2"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1832,18 +1803,18 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" ht="13">
       <c r="A24" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>83</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="1"/>
@@ -1861,18 +1832,18 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" ht="14.25">
       <c r="A25" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="C25" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="D25" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>88</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>55</v>
@@ -1890,24 +1861,24 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" ht="14.25">
       <c r="A26" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="D26" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="19" t="s">
         <v>91</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>92</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1921,18 +1892,18 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" ht="14.25">
       <c r="A27" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="D27" s="22" t="s">
         <v>94</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>95</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>55</v>
@@ -1950,24 +1921,24 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" ht="14.25">
       <c r="A28" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="19" t="s">
         <v>96</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>97</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -1981,18 +1952,18 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" ht="14.25">
       <c r="A29" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="D29" s="21" t="s">
         <v>99</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>100</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>55</v>
@@ -2010,24 +1981,24 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" ht="14.25">
       <c r="A30" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>101</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>102</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2041,18 +2012,18 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" ht="14.25">
       <c r="A31" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="D31" s="22" t="s">
         <v>104</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>105</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>55</v>
@@ -2070,24 +2041,24 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" ht="14.25">
       <c r="A32" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>106</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>107</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2101,18 +2072,18 @@
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" ht="13">
       <c r="A33" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="C33" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="D33" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>55</v>
@@ -2130,24 +2101,24 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" ht="14.25">
       <c r="A34" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B34" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>112</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>113</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2161,18 +2132,18 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:17" ht="14.25">
       <c r="A35" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="C35" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="D35" s="22" t="s">
         <v>116</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>117</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>55</v>
@@ -2190,24 +2161,24 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" ht="14.25">
       <c r="A36" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B36" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="19" t="s">
         <v>118</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>119</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2221,14 +2192,15 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:17" ht="13">
       <c r="A37" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="C37" s="35"/>
+      <c r="D37" s="36"/>
       <c r="E37" s="2"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -2243,18 +2215,18 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:17" ht="13">
       <c r="A38" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="D38" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="12" t="s">
@@ -2271,18 +2243,18 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:17" ht="14.25">
       <c r="A39" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="D39" s="22" t="s">
         <v>124</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>125</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>55</v>
@@ -2300,24 +2272,24 @@
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:17" ht="14.25">
       <c r="A40" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>127</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2331,18 +2303,18 @@
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:17" ht="14.25">
       <c r="A41" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="D41" s="22" t="s">
         <v>129</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>130</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>55</v>
@@ -2360,24 +2332,24 @@
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:17" ht="14.25">
       <c r="A42" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>131</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>132</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2391,18 +2363,18 @@
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:17" ht="14.25">
       <c r="A43" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B43" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="D43" s="21" t="s">
         <v>134</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>135</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>55</v>
@@ -2420,24 +2392,24 @@
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:17" ht="14.25">
       <c r="A44" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B44" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="19" t="s">
         <v>136</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>137</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2451,43 +2423,43 @@
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:17" ht="13">
       <c r="A45" s="24" t="s">
         <v>27</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="13">
       <c r="A46" s="24" t="s">
         <v>17</v>
       </c>
       <c r="B46" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="D46" s="24" t="s">
         <v>139</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>140</v>
       </c>
       <c r="G46" s="24" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:17" ht="14.25">
       <c r="A47" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B47" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="D47" s="22" t="s">
         <v>142</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>143</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>55</v>
@@ -2505,24 +2477,24 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:17" ht="14.25">
       <c r="A48" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="19" t="s">
         <v>144</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>145</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2536,18 +2508,18 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:17" ht="13">
       <c r="A49" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="D49" s="21" t="s">
         <v>147</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>148</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>55</v>
@@ -2565,24 +2537,24 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:17" ht="14.25">
       <c r="A50" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B50" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="19" t="s">
         <v>149</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>150</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2596,18 +2568,18 @@
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:17" ht="13">
       <c r="A51" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="D51" s="21" t="s">
         <v>152</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>55</v>
@@ -2625,24 +2597,24 @@
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:17" ht="14.25">
       <c r="A52" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="19" t="s">
         <v>154</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>155</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2656,18 +2628,18 @@
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:17" ht="14.25">
       <c r="A53" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B53" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="D53" s="21" t="s">
         <v>157</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>158</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>55</v>
@@ -2685,24 +2657,24 @@
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:17" ht="14.25">
       <c r="A54" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B54" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54" s="19" t="s">
         <v>159</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>160</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2716,124 +2688,124 @@
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:17" ht="13">
       <c r="A55" s="24" t="s">
         <v>27</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="13">
       <c r="A56" s="24" t="s">
         <v>17</v>
       </c>
       <c r="B56" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="D56" s="24" t="s">
         <v>162</v>
-      </c>
-      <c r="D56" s="24" t="s">
-        <v>163</v>
       </c>
       <c r="G56" s="24" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:17" ht="13">
       <c r="A57" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="24" t="s">
+      <c r="C57" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="D57" s="24" t="s">
         <v>166</v>
-      </c>
-      <c r="D57" s="24" t="s">
-        <v>167</v>
       </c>
       <c r="E57" s="24" t="s">
         <v>55</v>
       </c>
       <c r="F57" s="24"/>
       <c r="I57" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="J57" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="J57" s="20" t="s">
+      <c r="K57" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="K57" s="26" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58">
+    </row>
+    <row r="58" spans="1:17" ht="13">
       <c r="A58" s="24" t="s">
         <v>51</v>
       </c>
       <c r="B58" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C58" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="D58" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="D58" s="24" t="s">
+      <c r="E58" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="E58" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F58" s="27" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="1:17" ht="13">
       <c r="A59" s="24" t="s">
         <v>51</v>
       </c>
       <c r="B59" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="D59" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D59" s="24" t="s">
+      <c r="E59" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="E59" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F59" s="27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="1:17" ht="13">
       <c r="A60" s="24" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="D60" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="D60" s="24" t="s">
+      <c r="E60" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="E60" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F60" s="27" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" spans="1:17" ht="13">
       <c r="A61" s="24" t="s">
         <v>27</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2841,23 +2813,24 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C37:D37"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.29"/>
+    <col min="1" max="1" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1" s="29" t="s">
         <v>1</v>
@@ -2869,278 +2842,279 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="24" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="24" t="s">
+      <c r="C3" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="D5" s="24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13">
+      <c r="A6" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13">
+      <c r="A7" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13">
+      <c r="A8" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13">
+      <c r="A9" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13">
+      <c r="A10" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13">
+      <c r="A11" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13">
+      <c r="A12" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="D12" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="24" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="13">
+      <c r="A13" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="s">
+      <c r="C13" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="13">
+      <c r="A14" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="13">
+      <c r="A15" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="D15" s="24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="13">
+      <c r="A16" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="13">
+      <c r="A17" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" s="24" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="13">
+      <c r="A18" s="24" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="s">
+      <c r="B18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>211</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.43"/>
-    <col customWidth="1" min="2" max="2" width="20.29"/>
+    <col min="1" max="1" width="19.40625" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="C1" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="E1" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="F1" s="32" t="s">
         <v>216</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>217</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -3163,18 +3137,19 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="E2" s="34" t="s">
         <v>220</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>221</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -3202,6 +3177,6 @@
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/forms/app/peer_mentor_checklist.xlsx
+++ b/forms/app/peer_mentor_checklist.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F582975-9C4A-4389-854F-65ED9DDFD820}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="4425" windowHeight="2115"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="4425" windowHeight="2115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="223">
   <si>
     <t>type</t>
   </si>
@@ -255,9 +256,6 @@
     <t>Nambari ya simu ya CHV</t>
   </si>
   <si>
-    <t>numbers</t>
-  </si>
-  <si>
     <t>Use the following format 0XXXXXXXXX</t>
   </si>
   <si>
@@ -702,13 +700,19 @@
     <t>data</t>
   </si>
   <si>
-    <t>tel</t>
+    <t>regex(.,'^[0oO][0-9oO]{9}$')</t>
+  </si>
+  <si>
+    <t>phone_raw</t>
+  </si>
+  <si>
+    <t>translate (translate (${phone_raw}, "o","0"), "O","0")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12">
     <font>
       <sz val="10"/>
@@ -719,15 +723,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -748,25 +755,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -814,10 +826,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -861,10 +874,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{CED25B55-B2F7-42A5-AF1E-C230C63E7194}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1076,11 +1094,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z61"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1709,11 +1727,11 @@
       <c r="Z20" s="14"/>
     </row>
     <row r="21" spans="1:26" ht="13">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="37" t="s">
         <v>221</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>70</v>
@@ -1725,18 +1743,16 @@
         <v>55</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="15"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="J21" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" s="15" t="s">
+      <c r="K21" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>74</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1745,58 +1761,69 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="13">
-      <c r="A22" s="12" t="s">
-        <v>51</v>
+    <row r="22" spans="1:26" s="36" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A22" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="L22" s="18"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
     </row>
     <row r="23" spans="1:26" ht="13">
       <c r="A23" s="12" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="I23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L23" s="18"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -1805,51 +1832,45 @@
     </row>
     <row r="24" spans="1:26" ht="13">
       <c r="A24" s="12" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>83</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C24" s="39"/>
+      <c r="D24" s="40"/>
       <c r="E24" s="2"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="19" t="s">
-        <v>50</v>
-      </c>
+      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="5"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="14.25">
-      <c r="A25" s="20" t="s">
-        <v>84</v>
+    <row r="25" spans="1:26" ht="13">
+      <c r="A25" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>55</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="2"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="19" t="s">
+        <v>50</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1863,29 +1884,27 @@
     </row>
     <row r="26" spans="1:26" ht="14.25">
       <c r="A26" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="19" t="s">
-        <v>91</v>
-      </c>
+      <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1894,21 +1913,23 @@
     </row>
     <row r="27" spans="1:26" ht="14.25">
       <c r="A27" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="1"/>
+      <c r="F27" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="2"/>
@@ -1923,23 +1944,21 @@
     </row>
     <row r="28" spans="1:26" ht="14.25">
       <c r="A28" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="19" t="s">
-        <v>96</v>
-      </c>
+      <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="2"/>
@@ -1954,21 +1973,23 @@
     </row>
     <row r="29" spans="1:26" ht="14.25">
       <c r="A29" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="19" t="s">
+        <v>95</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="2"/>
@@ -1983,23 +2004,21 @@
     </row>
     <row r="30" spans="1:26" ht="14.25">
       <c r="A30" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>90</v>
+        <v>97</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>98</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>101</v>
-      </c>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="2"/>
@@ -2014,27 +2033,29 @@
     </row>
     <row r="31" spans="1:26" ht="14.25">
       <c r="A31" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="19" t="s">
+        <v>100</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="5"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -2043,89 +2064,87 @@
     </row>
     <row r="32" spans="1:26" ht="14.25">
       <c r="A32" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>106</v>
-      </c>
+      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="5"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="13">
-      <c r="A33" s="23" t="s">
-        <v>107</v>
+    <row r="33" spans="1:17" ht="14.25">
+      <c r="A33" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="5"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" ht="14.25">
-      <c r="A34" s="20" t="s">
-        <v>51</v>
+    <row r="34" spans="1:17" ht="13">
+      <c r="A34" s="23" t="s">
+        <v>106</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>90</v>
+        <v>107</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>112</v>
-      </c>
+      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="5"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -2133,26 +2152,28 @@
       <c r="Q34" s="1"/>
     </row>
     <row r="35" spans="1:17" ht="14.25">
-      <c r="A35" s="23" t="s">
-        <v>113</v>
+      <c r="A35" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>88</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="19" t="s">
+        <v>111</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2162,28 +2183,26 @@
       <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="1:17" ht="14.25">
-      <c r="A36" s="20" t="s">
-        <v>51</v>
+      <c r="A36" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>89</v>
+        <v>113</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="19" t="s">
-        <v>118</v>
-      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -2192,21 +2211,29 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" ht="13">
-      <c r="A37" s="12" t="s">
-        <v>27</v>
+    <row r="37" spans="1:17" ht="14.25">
+      <c r="A37" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>117</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2217,50 +2244,44 @@
     </row>
     <row r="38" spans="1:17" ht="13">
       <c r="A38" s="12" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>121</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="2"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="12" t="s">
-        <v>50</v>
-      </c>
+      <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="5"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" ht="14.25">
-      <c r="A39" s="20" t="s">
-        <v>84</v>
+    <row r="39" spans="1:17" ht="13">
+      <c r="A39" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>55</v>
+        <v>118</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="G39" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -2274,29 +2295,27 @@
     </row>
     <row r="40" spans="1:17" ht="14.25">
       <c r="A40" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>126</v>
-      </c>
+      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="5"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -2305,27 +2324,29 @@
     </row>
     <row r="41" spans="1:17" ht="14.25">
       <c r="A41" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="1"/>
+      <c r="F41" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="5"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
@@ -2334,29 +2355,27 @@
     </row>
     <row r="42" spans="1:17" ht="14.25">
       <c r="A42" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="19" t="s">
-        <v>131</v>
-      </c>
+      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="5"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -2365,27 +2384,29 @@
     </row>
     <row r="43" spans="1:17" ht="14.25">
       <c r="A43" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>134</v>
+        <v>88</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="1"/>
+      <c r="F43" s="19" t="s">
+        <v>130</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="5"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -2394,234 +2415,232 @@
     </row>
     <row r="44" spans="1:17" ht="14.25">
       <c r="A44" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>90</v>
+        <v>132</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>133</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F44" s="19" t="s">
-        <v>136</v>
-      </c>
+      <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="5"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" spans="1:17" ht="13">
-      <c r="A45" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>119</v>
-      </c>
+    <row r="45" spans="1:17" ht="14.25">
+      <c r="A45" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:17" ht="13">
       <c r="A46" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="13">
+      <c r="A47" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B47" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="D47" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="G46" s="24" t="s">
+      <c r="G47" s="24" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" ht="14.25">
-      <c r="A47" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
     </row>
     <row r="48" spans="1:17" ht="14.25">
       <c r="A48" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>89</v>
+        <v>139</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="19" t="s">
-        <v>144</v>
-      </c>
+      <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="5"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:17" ht="13">
+    <row r="49" spans="1:17" ht="14.25">
       <c r="A49" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>147</v>
+        <v>142</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="1"/>
+      <c r="F49" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="5"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:17" ht="14.25">
+    <row r="50" spans="1:17" ht="13">
       <c r="A50" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>90</v>
+        <v>144</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>146</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F50" s="19" t="s">
-        <v>149</v>
-      </c>
+      <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="5"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:17" ht="13">
+    <row r="51" spans="1:17" ht="14.25">
       <c r="A51" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>152</v>
+        <v>147</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="1"/>
+      <c r="F51" s="19" t="s">
+        <v>148</v>
+      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="5"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:17" ht="14.25">
+    <row r="52" spans="1:17" ht="13">
       <c r="A52" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>90</v>
+        <v>149</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>151</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F52" s="19" t="s">
-        <v>154</v>
-      </c>
+      <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="5"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -2630,27 +2649,29 @@
     </row>
     <row r="53" spans="1:17" ht="14.25">
       <c r="A53" s="20" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>157</v>
+        <v>88</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>89</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F53" s="1"/>
+      <c r="F53" s="19" t="s">
+        <v>153</v>
+      </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="5"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -2659,105 +2680,114 @@
     </row>
     <row r="54" spans="1:17" ht="14.25">
       <c r="A54" s="20" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>90</v>
+        <v>155</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="19" t="s">
-        <v>159</v>
-      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="5"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" ht="13">
-      <c r="A55" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>137</v>
-      </c>
+    <row r="55" spans="1:17" ht="14.25">
+      <c r="A55" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
     </row>
     <row r="56" spans="1:17" ht="13">
       <c r="A56" s="24" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="D56" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="G56" s="24" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="13">
       <c r="A57" s="24" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E57" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F57" s="24"/>
-      <c r="I57" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="J57" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="K57" s="26" t="s">
-        <v>169</v>
+        <v>161</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="13">
       <c r="A58" s="24" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F58" s="27" t="s">
-        <v>173</v>
+      <c r="F58" s="24"/>
+      <c r="I58" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="K58" s="26" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="13">
@@ -2765,19 +2795,19 @@
         <v>51</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>55</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="13">
@@ -2785,40 +2815,60 @@
         <v>51</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>55</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="13">
       <c r="A61" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" s="27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="13">
+      <c r="A62" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="24" t="s">
-        <v>160</v>
+      <c r="B62" s="24" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C38:D38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2828,9 +2878,9 @@
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="15.25">
       <c r="A1" s="28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1" s="29" t="s">
         <v>1</v>
@@ -2844,240 +2894,240 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>184</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="D3" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="D4" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>55</v>
       </c>
       <c r="C5" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>184</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="13">
       <c r="A6" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="13">
       <c r="A7" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B7" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D7" s="24" t="s">
         <v>194</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="13">
       <c r="A8" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="24" t="s">
         <v>197</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="13">
       <c r="A9" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>200</v>
-      </c>
       <c r="D9" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="13">
       <c r="A10" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B10" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="D10" s="24" t="s">
         <v>202</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="13">
       <c r="A11" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="30" t="s">
         <v>184</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13">
       <c r="A12" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="D12" s="30" t="s">
         <v>187</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="13">
       <c r="A13" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="D13" s="30" t="s">
         <v>190</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="13">
       <c r="A14" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="D14" s="24" t="s">
         <v>205</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="13">
       <c r="A15" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>184</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="13">
       <c r="A16" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B16" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="D16" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="13">
       <c r="A17" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="13">
       <c r="A18" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="30" t="s">
         <v>209</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3086,7 +3136,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -3099,22 +3149,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="C1" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="E1" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="F1" s="32" t="s">
         <v>215</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>216</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -3139,17 +3189,17 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="34" t="s">
+      <c r="E2" s="34" t="s">
         <v>219</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>220</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>

--- a/forms/app/peer_mentor_checklist.xlsx
+++ b/forms/app/peer_mentor_checklist.xlsx
@@ -1,23 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F582975-9C4A-4389-854F-65ED9DDFD820}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="4425" windowHeight="2115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="kDxcMOcElwFiXNHFoU5DSmbEEr9vOzioLvqDhvlR14o="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -174,8 +170,7 @@
 •        Epuka mikusanyiko. 
 •        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
 •        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
-•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
-</t>
+•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">end group </t>
@@ -247,19 +242,28 @@
     <t>Jaza jina la babu</t>
   </si>
   <si>
+    <t>phone_raw</t>
+  </si>
+  <si>
+    <t>CHV phone</t>
+  </si>
+  <si>
+    <t>Nambari ya simu ya CHV</t>
+  </si>
+  <si>
+    <t>regex(.,'^[0oO][0-9oO]{9}$')</t>
+  </si>
+  <si>
+    <t>Use the following format 0XXXXXXXXX</t>
+  </si>
+  <si>
+    <t>Tumia mfumo huu 0XXXXXXXXX.</t>
+  </si>
+  <si>
     <t>phone</t>
   </si>
   <si>
-    <t>CHV phone</t>
-  </si>
-  <si>
-    <t>Nambari ya simu ya CHV</t>
-  </si>
-  <si>
-    <t>Use the following format 0XXXXXXXXX</t>
-  </si>
-  <si>
-    <t>Tumia mfumo huu 0XXXXXXXXX.</t>
+    <t>translate (translate (${phone_raw}, "o","0"), "O","0")</t>
   </si>
   <si>
     <t>shehia</t>
@@ -698,87 +702,63 @@
   </si>
   <si>
     <t>data</t>
-  </si>
-  <si>
-    <t>regex(.,'^[0oO][0-9oO]{9}$')</t>
-  </si>
-  <si>
-    <t>phone_raw</t>
-  </si>
-  <si>
-    <t>translate (translate (${phone_raw}, "o","0"), "O","0")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="10">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10.0"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Lato"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1D1C1D"/>
-      <name val="Slack-Lato"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -786,7 +766,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -802,103 +782,71 @@
     </fill>
   </fills>
   <borders count="3">
+    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="16">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{CED25B55-B2F7-42A5-AF1E-C230C63E7194}"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1088,29 +1036,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z62"/>
-  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="27.40625" customWidth="1"/>
-    <col min="3" max="3" width="57" customWidth="1"/>
-    <col min="4" max="4" width="34.40625" customWidth="1"/>
-    <col min="5" max="5" width="22.26953125" customWidth="1"/>
-    <col min="9" max="9" width="36.1328125" customWidth="1"/>
-    <col min="10" max="10" width="29.40625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="24.0"/>
+    <col customWidth="1" min="2" max="2" width="27.38"/>
+    <col customWidth="1" min="3" max="3" width="57.0"/>
+    <col customWidth="1" min="4" max="4" width="34.38"/>
+    <col customWidth="1" min="5" max="5" width="22.25"/>
+    <col customWidth="1" min="6" max="8" width="14.38"/>
+    <col customWidth="1" min="9" max="9" width="36.13"/>
+    <col customWidth="1" min="10" max="10" width="29.38"/>
+    <col customWidth="1" min="11" max="26" width="14.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="13">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="13">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1191,7 +1139,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="13">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1216,7 +1164,7 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="13">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1241,7 +1189,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="13">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -1266,7 +1214,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="13">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1291,7 +1239,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="13">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1314,7 +1262,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="13">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -1337,7 +1285,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="13">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -1355,7 +1303,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="M9" s="1"/>
@@ -1364,11 +1312,11 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="13">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="1"/>
@@ -1382,7 +1330,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M10" s="1"/>
@@ -1391,7 +1339,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="13">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1409,7 +1357,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="M11" s="1"/>
@@ -1418,164 +1366,164 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="13">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-    </row>
-    <row r="13" spans="1:26" ht="13">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-    </row>
-    <row r="14" spans="1:26" ht="13">
-      <c r="A14" s="8" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-    </row>
-    <row r="15" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A15" s="8" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-    </row>
-    <row r="16" spans="1:26" ht="13">
-      <c r="A16" s="8" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-    </row>
-    <row r="17" spans="1:26" ht="13">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E17" s="1"/>
@@ -1594,165 +1542,165 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="13">
-      <c r="A18" s="13" t="s">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="13" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-    </row>
-    <row r="19" spans="1:26" ht="13">
-      <c r="A19" s="13" t="s">
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="13" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-    </row>
-    <row r="20" spans="1:26" ht="13">
-      <c r="A20" s="13" t="s">
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="13" t="s">
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-    </row>
-    <row r="21" spans="1:26" ht="13">
-      <c r="A21" s="35" t="s">
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="B21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="15"/>
+      <c r="G21" s="2"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="J21" s="15" t="s">
+      <c r="I21" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="J21" s="2" t="s">
         <v>73</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1761,84 +1709,83 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:26" s="36" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A22" s="14" t="s">
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-    </row>
-    <row r="23" spans="1:26" ht="13">
-      <c r="A23" s="12" t="s">
+      <c r="B22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="12" t="s">
+      <c r="B23" s="2" t="s">
         <v>77</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="L23" s="18"/>
+      <c r="J23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L23" s="8"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="13">
-      <c r="A24" s="12" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
+      <c r="C24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1853,49 +1800,49 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="13">
-      <c r="A25" s="12" t="s">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>82</v>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="5"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="14.25">
-      <c r="A26" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="22" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="B26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F26" s="1"/>
@@ -1903,32 +1850,32 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="5"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="14.25">
-      <c r="A27" s="20" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="12" t="s">
+      <c r="B27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="19" t="s">
-        <v>90</v>
+      <c r="F27" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1942,20 +1889,20 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25">
-      <c r="A28" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="12" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="1"/>
@@ -1971,24 +1918,24 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25">
-      <c r="A29" s="20" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="12" t="s">
+      <c r="B29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="19" t="s">
-        <v>95</v>
+      <c r="F29" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -2002,20 +1949,20 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25">
-      <c r="A30" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="12" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F30" s="1"/>
@@ -2031,24 +1978,24 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="14.25">
-      <c r="A31" s="20" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="12" t="s">
+      <c r="B31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>100</v>
+      <c r="F31" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2062,20 +2009,20 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25">
-      <c r="A32" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="12" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F32" s="1"/>
@@ -2083,32 +2030,32 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="5"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="14.25">
-      <c r="A33" s="20" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="12" t="s">
+      <c r="B33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="19" t="s">
-        <v>105</v>
+      <c r="F33" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2122,20 +2069,20 @@
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" ht="13">
-      <c r="A34" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="21" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="B34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F34" s="1"/>
@@ -2143,32 +2090,32 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="5"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" ht="14.25">
-      <c r="A35" s="20" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E35" s="12" t="s">
+      <c r="B35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="19" t="s">
-        <v>111</v>
+      <c r="F35" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2182,20 +2129,20 @@
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" ht="14.25">
-      <c r="A36" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" s="22" t="s">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="B36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F36" s="1"/>
@@ -2211,24 +2158,24 @@
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" ht="14.25">
-      <c r="A37" s="20" t="s">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="12" t="s">
+      <c r="B37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>117</v>
+      <c r="F37" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2242,15 +2189,14 @@
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" ht="13">
-      <c r="A38" s="12" t="s">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2265,48 +2211,48 @@
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" ht="13">
-      <c r="A39" s="12" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>120</v>
+      <c r="B39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="F39" s="1"/>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="2" t="s">
         <v>50</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="5"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" ht="14.25">
-      <c r="A40" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" s="12" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F40" s="1"/>
@@ -2314,32 +2260,32 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="5"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
     </row>
-    <row r="41" spans="1:17" ht="14.25">
-      <c r="A41" s="20" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E41" s="12" t="s">
+      <c r="B41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="19" t="s">
-        <v>125</v>
+      <c r="F41" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2353,20 +2299,20 @@
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
     </row>
-    <row r="42" spans="1:17" ht="14.25">
-      <c r="A42" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" s="12" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F42" s="1"/>
@@ -2374,32 +2320,32 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="5"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43" spans="1:17" ht="14.25">
-      <c r="A43" s="20" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E43" s="12" t="s">
+      <c r="B43" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="19" t="s">
-        <v>130</v>
+      <c r="F43" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -2413,20 +2359,20 @@
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
     </row>
-    <row r="44" spans="1:17" ht="14.25">
-      <c r="A44" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" s="12" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F44" s="1"/>
@@ -2434,32 +2380,32 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="5"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" spans="1:17" ht="14.25">
-      <c r="A45" s="20" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E45" s="12" t="s">
+      <c r="B45" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F45" s="19" t="s">
-        <v>135</v>
+      <c r="F45" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2473,45 +2419,45 @@
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
     </row>
-    <row r="46" spans="1:17" ht="13">
-      <c r="A46" s="24" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="13">
-      <c r="A47" s="24" t="s">
+      <c r="B46" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="G47" s="24" t="s">
+      <c r="B47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="14.25">
-      <c r="A48" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" s="12" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F48" s="1"/>
@@ -2519,32 +2465,32 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="5"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:17" ht="14.25">
-      <c r="A49" s="20" t="s">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E49" s="12" t="s">
+      <c r="B49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="19" t="s">
-        <v>143</v>
+      <c r="F49" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2558,20 +2504,20 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:17" ht="13">
-      <c r="A50" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E50" s="12" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F50" s="1"/>
@@ -2579,32 +2525,32 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="5"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:17" ht="14.25">
-      <c r="A51" s="20" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E51" s="12" t="s">
+      <c r="B51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="19" t="s">
-        <v>148</v>
+      <c r="F51" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2618,20 +2564,20 @@
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:17" ht="13">
-      <c r="A52" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" s="12" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F52" s="1"/>
@@ -2639,32 +2585,32 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="5"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:17" ht="14.25">
-      <c r="A53" s="20" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E53" s="12" t="s">
+      <c r="B53" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F53" s="19" t="s">
-        <v>153</v>
+      <c r="F53" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2678,20 +2624,20 @@
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:17" ht="14.25">
-      <c r="A54" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E54" s="12" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F54" s="1"/>
@@ -2699,32 +2645,32 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="5"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" ht="14.25">
-      <c r="A55" s="20" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="12" t="s">
+      <c r="B55" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="19" t="s">
-        <v>158</v>
+      <c r="F55" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2738,433 +2684,2361 @@
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:17" ht="13">
-      <c r="A56" s="24" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="13">
-      <c r="A57" s="24" t="s">
+      <c r="B56" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D57" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="G57" s="24" t="s">
+      <c r="B57" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="13">
-      <c r="A58" s="24" t="s">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="I58" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B58" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="D58" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="E58" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F58" s="24"/>
-      <c r="I58" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="J58" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="K58" s="26" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="13">
-      <c r="A59" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="D59" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F59" s="27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="13">
-      <c r="A60" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="C60" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D60" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="E60" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F60" s="27" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="13">
-      <c r="A61" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="E61" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F61" s="27" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="13">
-      <c r="A62" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>159</v>
-      </c>
-    </row>
+    </row>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C38:D38"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="18.25"/>
+    <col customWidth="1" min="2" max="26" width="14.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.25">
-      <c r="A1" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="29" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="24" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="24" t="s">
+      <c r="C2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="B3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D5" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="24" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C12" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D12" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="24" t="s">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="C13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="13">
-      <c r="A6" s="24" t="s">
+      <c r="C15" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="13">
-      <c r="A7" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="24" t="s">
+      <c r="C17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D17" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="13">
-      <c r="A8" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="13">
-      <c r="A9" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="13">
-      <c r="A10" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="13">
-      <c r="A11" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="13">
-      <c r="A12" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="13">
-      <c r="A13" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="13">
-      <c r="A14" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="13">
-      <c r="A15" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="13">
-      <c r="A16" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="13">
-      <c r="A17" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="13">
-      <c r="A18" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="30" t="s">
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
+      <c r="B18" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
-  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.40625" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="19.38"/>
+    <col customWidth="1" min="2" max="2" width="20.25"/>
+    <col customWidth="1" min="3" max="26" width="14.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" s="31" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="B1" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="C1" s="14" t="s">
         <v>215</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>218</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -3187,19 +5061,18 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A2" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="E2" s="34" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>219</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>222</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -3223,10 +5096,1011 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
+    <row r="3" ht="15.75" customHeight="1"/>
+    <row r="4" ht="15.75" customHeight="1"/>
+    <row r="5" ht="15.75" customHeight="1"/>
+    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>